--- a/data/incoming/question_metadata.xlsx
+++ b/data/incoming/question_metadata.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Database_for_human_hair_research\data\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94AA940-C56E-4748-9D41-9FD14785F030}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B3A772-F7DF-4315-A7D5-7CEDFDDABDA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AQ" sheetId="2" r:id="rId1"/>
-    <sheet name="demog-health" sheetId="3" r:id="rId2"/>
-    <sheet name="DERS" sheetId="4" r:id="rId3"/>
-    <sheet name="IPIP" sheetId="5" r:id="rId4"/>
-    <sheet name="lonliness" sheetId="6" r:id="rId5"/>
-    <sheet name="PCL" sheetId="7" r:id="rId6"/>
-    <sheet name="PSS" sheetId="8" r:id="rId7"/>
-    <sheet name="STAI" sheetId="9" r:id="rId8"/>
-    <sheet name="PHQ" sheetId="10" r:id="rId9"/>
+    <sheet name="AQ" sheetId="1" r:id="rId1"/>
+    <sheet name="demog-health" sheetId="2" r:id="rId2"/>
+    <sheet name="DERS" sheetId="3" r:id="rId3"/>
+    <sheet name="IPIP" sheetId="4" r:id="rId4"/>
+    <sheet name="lonliness" sheetId="5" r:id="rId5"/>
+    <sheet name="PCL" sheetId="6" r:id="rId6"/>
+    <sheet name="PSS" sheetId="7" r:id="rId7"/>
+    <sheet name="STAI" sheetId="8" r:id="rId8"/>
+    <sheet name="PHQ" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -69,730 +69,733 @@
     <t>אני מעדיף לעשות דברים יחד עם אחרים ולא לבדי</t>
   </si>
   <si>
+    <t>second-questionnaire</t>
+  </si>
+  <si>
+    <t>AQ</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>AQ_01</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Q20</t>
+  </si>
+  <si>
+    <t>אני מעדיף לעשות דברים באותו האופן שוב ושוב</t>
+  </si>
+  <si>
+    <t>AQ_02</t>
+  </si>
+  <si>
+    <t>Q21</t>
+  </si>
+  <si>
+    <t>כשאני מנסה לדמיין משהו, קל לי מאוד ליצור תמונה בראשי</t>
+  </si>
+  <si>
+    <t>AQ_03</t>
+  </si>
+  <si>
+    <t>Q22</t>
+  </si>
+  <si>
+    <t>לעתים קרובות אני שוקע עמוק כל-כך בדבר אחד עד שאני מפסיק לראות דברים אחרים</t>
+  </si>
+  <si>
+    <t>AQ_04</t>
+  </si>
+  <si>
+    <t>Q23</t>
+  </si>
+  <si>
+    <t>לעתים אני שם לב לקולות חלשים שאחרים אינם שמים לב אליהם</t>
+  </si>
+  <si>
+    <t>AQ_05</t>
+  </si>
+  <si>
+    <t>Q24</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני שם לב למספרי מכוניות או לפרטי מידע דומים</t>
+  </si>
+  <si>
+    <t>AQ_06</t>
+  </si>
+  <si>
+    <t>Q25</t>
+  </si>
+  <si>
+    <t>אנשים אומרים לי פעמים רבות שמה שאמרתי לא מנומס, אף על פי שלי נראה שהייתי מנומס</t>
+  </si>
+  <si>
+    <t>AQ_07</t>
+  </si>
+  <si>
+    <t>Q26</t>
+  </si>
+  <si>
+    <t>כשאני קורא סיפור אני יכול לדמיין לי בקלות איך נראות הדמויות</t>
+  </si>
+  <si>
+    <t>AQ_08</t>
+  </si>
+  <si>
+    <t>Q27</t>
+  </si>
+  <si>
+    <t>תאריכים מרתקים אותי</t>
+  </si>
+  <si>
+    <t>AQ_09</t>
+  </si>
+  <si>
+    <t>Q28</t>
+  </si>
+  <si>
+    <t>בקבוצה חברתית אני מסוגל בקלות לעקוב אחר כמה וכמה שיחות של אנשים</t>
+  </si>
+  <si>
+    <t>AQ_10</t>
+  </si>
+  <si>
+    <t>Q29</t>
+  </si>
+  <si>
+    <t>אני מסתדר בקלות בסיטואציות חברתיות</t>
+  </si>
+  <si>
+    <t>AQ_11</t>
+  </si>
+  <si>
+    <t>Q30</t>
+  </si>
+  <si>
+    <t>אני נוטה להבחין בפרטים שאחרים אינם מבחינים בהם</t>
+  </si>
+  <si>
+    <t>AQ_12</t>
+  </si>
+  <si>
+    <t>Q31</t>
+  </si>
+  <si>
+    <t>אני מעדיף בילוי בספרייה על פני בילוי במסיבה</t>
+  </si>
+  <si>
+    <t>AQ_13</t>
+  </si>
+  <si>
+    <t>Q32</t>
+  </si>
+  <si>
+    <t>קל לי להמציא סיפורים</t>
+  </si>
+  <si>
+    <t>AQ_14</t>
+  </si>
+  <si>
+    <t>Q33</t>
+  </si>
+  <si>
+    <t>אני נמשך לבני-אדם יותר מאשר לחפצים</t>
+  </si>
+  <si>
+    <t>AQ_15</t>
+  </si>
+  <si>
+    <t>Q34</t>
+  </si>
+  <si>
+    <t>יש לי תחומי עניין מוגדרים היטב ואני מתעצבן כשאני לא יכול לעסוק בהם</t>
+  </si>
+  <si>
+    <t>AQ_16</t>
+  </si>
+  <si>
+    <t>Q35</t>
+  </si>
+  <si>
+    <t>אני נהנה משיחת חולין חברתית</t>
+  </si>
+  <si>
+    <t>AQ_17</t>
+  </si>
+  <si>
+    <t>Q36</t>
+  </si>
+  <si>
+    <t>כשאני מדבר, לא תמיד קל לאחרים להשחיל מילה</t>
+  </si>
+  <si>
+    <t>AQ_18</t>
+  </si>
+  <si>
+    <t>Q37</t>
+  </si>
+  <si>
+    <t>מספרים מרתקים אותי</t>
+  </si>
+  <si>
+    <t>AQ_19</t>
+  </si>
+  <si>
+    <t>Q38</t>
+  </si>
+  <si>
+    <t>כשאני קורא סיפור, קשה לי להבין את כוונותיהן של הדמויות</t>
+  </si>
+  <si>
+    <t>AQ_20</t>
+  </si>
+  <si>
+    <t>Q39</t>
+  </si>
+  <si>
+    <t>אני לא כל-כך נהנה לקרוא ספרות יפה</t>
+  </si>
+  <si>
+    <t>AQ_21</t>
+  </si>
+  <si>
+    <t>Q40</t>
+  </si>
+  <si>
+    <t>קשה לי לרכוש חברים חדשים</t>
+  </si>
+  <si>
+    <t>AQ_22</t>
+  </si>
+  <si>
+    <t>Q41</t>
+  </si>
+  <si>
+    <t>אני שם לב לדפוסים בכל מיני דברים כל הזמן</t>
+  </si>
+  <si>
+    <t>AQ_23</t>
+  </si>
+  <si>
+    <t>Q42</t>
+  </si>
+  <si>
+    <t>אני מעדיף בילוי בתיאטרון על פני בילוי במוזיאון</t>
+  </si>
+  <si>
+    <t>AQ_24</t>
+  </si>
+  <si>
+    <t>Q43</t>
+  </si>
+  <si>
+    <t>אני לא מוטרד כששגרת היום שלי מופרת</t>
+  </si>
+  <si>
+    <t>AQ_25</t>
+  </si>
+  <si>
+    <t>Q44</t>
+  </si>
+  <si>
+    <t>לעתים קרובות מתברר לי שאני לא יודע להחזיק שיחה שלא תדעך</t>
+  </si>
+  <si>
+    <t>AQ_26</t>
+  </si>
+  <si>
+    <t>Q45</t>
+  </si>
+  <si>
+    <t>קל לי "לקרוא בין השורות" כשמישהו מדבר אלי</t>
+  </si>
+  <si>
+    <t>AQ_27</t>
+  </si>
+  <si>
+    <t>Q46</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני מתרכז בתמונה כולה ולא בפרטים הקטנים</t>
+  </si>
+  <si>
+    <t>AQ_28</t>
+  </si>
+  <si>
+    <t>Q47</t>
+  </si>
+  <si>
+    <t>אין לי זיכרון טוב למספרי טלפון</t>
+  </si>
+  <si>
+    <t>AQ_29</t>
+  </si>
+  <si>
+    <t>Q48</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני לא מבחין בשינויים קלים בסיטואציה או במראהו של אדם אחר</t>
+  </si>
+  <si>
+    <t>AQ_30</t>
+  </si>
+  <si>
+    <t>Q49</t>
+  </si>
+  <si>
+    <t>אני מבחין מיד כשאדם שמקשיב לי מתחיל להשתעמם</t>
+  </si>
+  <si>
+    <t>AQ_31</t>
+  </si>
+  <si>
+    <t>Q50</t>
+  </si>
+  <si>
+    <t>קל לי לעשות כמה דברים בבת אחת</t>
+  </si>
+  <si>
+    <t>AQ_32</t>
+  </si>
+  <si>
+    <t>Q51</t>
+  </si>
+  <si>
+    <t>כשאני מדבר בטלפון, אני לא בטוח מתי תורי לדבר</t>
+  </si>
+  <si>
+    <t>AQ_33</t>
+  </si>
+  <si>
+    <t>Q52</t>
+  </si>
+  <si>
+    <t>אני נהנה לעשות דברים באופן ספונטני</t>
+  </si>
+  <si>
+    <t>AQ_34</t>
+  </si>
+  <si>
+    <t>Q53</t>
+  </si>
+  <si>
+    <t>לא פעם אני האחרון שמבין בדיחה</t>
+  </si>
+  <si>
+    <t>AQ_35</t>
+  </si>
+  <si>
+    <t>Q54</t>
+  </si>
+  <si>
+    <t>אני מבחין בקלות מה אדם אחר חושב או מרגיש ממראה פניו בלבד</t>
+  </si>
+  <si>
+    <t>AQ_36</t>
+  </si>
+  <si>
+    <t>Q55</t>
+  </si>
+  <si>
+    <t>כשמפריעים לי, אני יכול לחזור למה שעשיתי לפני כן במהירות רבה</t>
+  </si>
+  <si>
+    <t>AQ_37</t>
+  </si>
+  <si>
+    <t>Q56</t>
+  </si>
+  <si>
+    <t>אני טוב בשיחת חולין חברתית</t>
+  </si>
+  <si>
+    <t>AQ_38</t>
+  </si>
+  <si>
+    <t>Q57</t>
+  </si>
+  <si>
+    <t>אנשים אומרים לי פעמים רבות שאני מדבר עוד ועוד על אותו הדבר</t>
+  </si>
+  <si>
+    <t>AQ_39</t>
+  </si>
+  <si>
+    <t>Q58</t>
+  </si>
+  <si>
+    <t>כשהייתי צעיר נהניתי לשחק עם ילדים אחרים במשחקי דימיון</t>
+  </si>
+  <si>
+    <t>AQ_40</t>
+  </si>
+  <si>
+    <t>Q59</t>
+  </si>
+  <si>
+    <t>('אני אוהב לאסוף מידע על סוגים של דברים (למשל, סוגי מכוניות, מיני ציפורים, סוגי רכבות, מיני צמחים וכו</t>
+  </si>
+  <si>
+    <t>AQ_41</t>
+  </si>
+  <si>
+    <t>Q60</t>
+  </si>
+  <si>
+    <t>קשה לי לדמיין איך זה להיות אדם אחר</t>
+  </si>
+  <si>
+    <t>AQ_42</t>
+  </si>
+  <si>
+    <t>Q61</t>
+  </si>
+  <si>
+    <t>אני אוהב לתכנן בקפידה כל פעילות שאני משתתף בה</t>
+  </si>
+  <si>
+    <t>AQ_43</t>
+  </si>
+  <si>
+    <t>Q62</t>
+  </si>
+  <si>
+    <t>אני נהנה מאירועים חברתיים</t>
+  </si>
+  <si>
+    <t>AQ_44</t>
+  </si>
+  <si>
+    <t>Q63</t>
+  </si>
+  <si>
+    <t>אני מתקשה להבין את כוונותיהם של אנשים אחרים</t>
+  </si>
+  <si>
+    <t>AQ_45</t>
+  </si>
+  <si>
+    <t>Q64</t>
+  </si>
+  <si>
+    <t>מצבים חדשים מעוררים בי חרדה</t>
+  </si>
+  <si>
+    <t>AQ_46</t>
+  </si>
+  <si>
+    <t>Q65</t>
+  </si>
+  <si>
+    <t>אני נהנה להכיר אנשים חדשים</t>
+  </si>
+  <si>
+    <t>AQ_47</t>
+  </si>
+  <si>
+    <t>Q66</t>
+  </si>
+  <si>
+    <t>אני דיפלומט טוב</t>
+  </si>
+  <si>
+    <t>AQ_48</t>
+  </si>
+  <si>
+    <t>Q67</t>
+  </si>
+  <si>
+    <t>אני לא מצטיין בזכירת ימי ההולדת של אנשים אחרים</t>
+  </si>
+  <si>
+    <t>AQ_49</t>
+  </si>
+  <si>
+    <t>Q68</t>
+  </si>
+  <si>
+    <t>קל לי מאוד לשחק עם ילדים במשחקים שכרוכים בהעמדת פנים</t>
+  </si>
+  <si>
+    <t>AQ_50</t>
+  </si>
+  <si>
+    <t>Q108</t>
+  </si>
+  <si>
+    <t>אני מעדיפה לעשות דברים יחד עם אחרים ולא לבדי</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>Q109</t>
+  </si>
+  <si>
+    <t>אני מעדיפה לעשות דברים באותו האופן שוב ושוב</t>
+  </si>
+  <si>
+    <t>Q110</t>
+  </si>
+  <si>
+    <t>Q111</t>
+  </si>
+  <si>
+    <t>לעתים קרובות אני שוקעת עמוק כל-כך בדבר אחד עד שאני מפסיקה לראות דברים אחרים</t>
+  </si>
+  <si>
+    <t>Q112</t>
+  </si>
+  <si>
+    <t>לעיתים אני שמה לב לקולות חלשים שאחרים אינם שמים לב אליהם</t>
+  </si>
+  <si>
+    <t>Q113</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני שמה לב למספרי מכוניות או לפרטי מידע דומים</t>
+  </si>
+  <si>
+    <t>Q114</t>
+  </si>
+  <si>
+    <t>אנשים אומרים לי פעמים רבות שמה שאמרתי לא מנומס, אף על פי שלי נראה שהייתי מנומסת</t>
+  </si>
+  <si>
+    <t>Q115</t>
+  </si>
+  <si>
+    <t>כשאני קוראת סיפור אני יכולה לדמיין לי בקלות איך נראות הדמויות</t>
+  </si>
+  <si>
+    <t>Q116</t>
+  </si>
+  <si>
+    <t>Q117</t>
+  </si>
+  <si>
+    <t>בקבוצה חברתית אני מסוגלת בקלות לעקוב אחר כמה וכמה שיחות של אנשים</t>
+  </si>
+  <si>
+    <t>Q118</t>
+  </si>
+  <si>
+    <t>אני מסתדרת בקלות בסיטואציות חברתיות</t>
+  </si>
+  <si>
+    <t>Q119</t>
+  </si>
+  <si>
+    <t>Q120</t>
+  </si>
+  <si>
+    <t>אני מעדיפה בילוי בספרייה על פני בילוי במסיבה</t>
+  </si>
+  <si>
+    <t>Q121</t>
+  </si>
+  <si>
+    <t>Q122</t>
+  </si>
+  <si>
+    <t>אני נמשכת לבני-אדם יותר מאשר לחפצים</t>
+  </si>
+  <si>
+    <t>Q123</t>
+  </si>
+  <si>
+    <t>יש לי תחומי עניין מוגדרים היטב ואני מתעצבנת כשאני לא יכולה לעסוק בהם</t>
+  </si>
+  <si>
+    <t>Q124</t>
+  </si>
+  <si>
+    <t>אני נהנית משיחת חולין חברתית</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>כשאני מדברת, לא תמיד קל לאחרים להשחיל מילה</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>כשאני קוראת סיפור, קשה לי להבין את כוונותיהן של הדמויות</t>
+  </si>
+  <si>
+    <t>Q128</t>
+  </si>
+  <si>
+    <t>אני לא כל-כך נהנת לקרוא ספרות יפה</t>
+  </si>
+  <si>
+    <t>Q129</t>
+  </si>
+  <si>
+    <t>Q130</t>
+  </si>
+  <si>
+    <t>אני שמה לב לדפוסים בכל מיני דברים כל הזמן</t>
+  </si>
+  <si>
+    <t>Q131</t>
+  </si>
+  <si>
+    <t>אני מעדיפה בילוי בתיאטרון על פני בילוי במוזיאון</t>
+  </si>
+  <si>
+    <t>Q132</t>
+  </si>
+  <si>
+    <t>אני לא מוטרדת כששגרת היום שלי מופרת</t>
+  </si>
+  <si>
+    <t>Q133</t>
+  </si>
+  <si>
+    <t>לעתים קרובות מתברר לי שאני לא יודעת להחזיק שיחה שלא תדעך</t>
+  </si>
+  <si>
+    <t>Q134</t>
+  </si>
+  <si>
+    <t>Q135</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני מתרכזת בתמונה כולה ולא בפרטים הקטנים</t>
+  </si>
+  <si>
+    <t>Q136</t>
+  </si>
+  <si>
+    <t>Q137</t>
+  </si>
+  <si>
+    <t>בדרך-כלל אני לא מבחינה בשינויים קלים בסיטואציה או במראהו של אדם אחר</t>
+  </si>
+  <si>
+    <t>Q138</t>
+  </si>
+  <si>
+    <t>אני מבחינה מיד כשאדם שמקשיב לי מתחיל להשתעמם</t>
+  </si>
+  <si>
+    <t>Q139</t>
+  </si>
+  <si>
+    <t>Q140</t>
+  </si>
+  <si>
+    <t>כשאני מדברת בטלפון, אני לא בטוחה מתי תורי לדבר</t>
+  </si>
+  <si>
+    <t>Q141</t>
+  </si>
+  <si>
+    <t>אני נהנת לעשות דברים באופן ספונטני</t>
+  </si>
+  <si>
+    <t>Q142</t>
+  </si>
+  <si>
+    <t>לא פעם אני האחרונה שמבינה בדיחה</t>
+  </si>
+  <si>
+    <t>Q143</t>
+  </si>
+  <si>
+    <t>אני מבחינה בקלות מה אדם אחר חושב או מרגיש ממראה פניו בלבד</t>
+  </si>
+  <si>
+    <t>Q144</t>
+  </si>
+  <si>
+    <t>כשמפריעים לי, אני יכולה לחזור למה שעשיתי לפני כן במהירות רבה</t>
+  </si>
+  <si>
+    <t>Q145</t>
+  </si>
+  <si>
+    <t>אני טובה בשיחת חולין חברתית</t>
+  </si>
+  <si>
+    <t>Q146</t>
+  </si>
+  <si>
+    <t>אנשים אומרים לי פעמים רבות שאני מדברת עוד ועוד על אותו הדבר</t>
+  </si>
+  <si>
+    <t>Q147</t>
+  </si>
+  <si>
+    <t>כשהייתי צעירה נהניתי לשחק עם ילדים אחרים במשחקי דמיון</t>
+  </si>
+  <si>
+    <t>Q148</t>
+  </si>
+  <si>
+    <t>('אני אוהבת לאסוף מידע על סוגים של דברים (למשל, סוגי מכוניות, מיני ציפורים, סוגי רכבות, מיני צמחים וכו</t>
+  </si>
+  <si>
+    <t>Q149</t>
+  </si>
+  <si>
+    <t>Q150</t>
+  </si>
+  <si>
+    <t>אני אוהבת לתכנן בקפידה כל פעילות שאני משתתפת בה</t>
+  </si>
+  <si>
+    <t>Q151</t>
+  </si>
+  <si>
+    <t>אני נהנית מאירועים חברתיים</t>
+  </si>
+  <si>
+    <t>Q152</t>
+  </si>
+  <si>
+    <t>Q153</t>
+  </si>
+  <si>
+    <t>Q154</t>
+  </si>
+  <si>
+    <t>אני נהנית להכיר אנשים חדשים</t>
+  </si>
+  <si>
+    <t>Q155</t>
+  </si>
+  <si>
+    <t>אני דיפלומטית טובה</t>
+  </si>
+  <si>
+    <t>Q156</t>
+  </si>
+  <si>
+    <t>אני לא מצטיינת בזכירת ימי ההולדת של אנשים אחרים</t>
+  </si>
+  <si>
+    <t>Q157</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>אנא הזינו את מספר הנבדק שקיבלתם במייל</t>
+  </si>
+  <si>
     <t>first-questionnaire</t>
-  </si>
-  <si>
-    <t>AQ</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>AQ_01</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>Q20</t>
-  </si>
-  <si>
-    <t>אני מעדיף לעשות דברים באותו האופן שוב ושוב</t>
-  </si>
-  <si>
-    <t>AQ_02</t>
-  </si>
-  <si>
-    <t>Q21</t>
-  </si>
-  <si>
-    <t>כשאני מנסה לדמיין משהו, קל לי מאוד ליצור תמונה בראשי</t>
-  </si>
-  <si>
-    <t>AQ_03</t>
-  </si>
-  <si>
-    <t>Q22</t>
-  </si>
-  <si>
-    <t>לעתים קרובות אני שוקע עמוק כל-כך בדבר אחד עד שאני מפסיק לראות דברים אחרים</t>
-  </si>
-  <si>
-    <t>AQ_04</t>
-  </si>
-  <si>
-    <t>Q23</t>
-  </si>
-  <si>
-    <t>לעתים אני שם לב לקולות חלשים שאחרים אינם שמים לב אליהם</t>
-  </si>
-  <si>
-    <t>AQ_05</t>
-  </si>
-  <si>
-    <t>Q24</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני שם לב למספרי מכוניות או לפרטי מידע דומים</t>
-  </si>
-  <si>
-    <t>AQ_06</t>
-  </si>
-  <si>
-    <t>Q25</t>
-  </si>
-  <si>
-    <t>אנשים אומרים לי פעמים רבות שמה שאמרתי לא מנומס, אף על פי שלי נראה שהייתי מנומס</t>
-  </si>
-  <si>
-    <t>AQ_07</t>
-  </si>
-  <si>
-    <t>Q26</t>
-  </si>
-  <si>
-    <t>כשאני קורא סיפור אני יכול לדמיין לי בקלות איך נראות הדמויות</t>
-  </si>
-  <si>
-    <t>AQ_08</t>
-  </si>
-  <si>
-    <t>Q27</t>
-  </si>
-  <si>
-    <t>תאריכים מרתקים אותי</t>
-  </si>
-  <si>
-    <t>AQ_09</t>
-  </si>
-  <si>
-    <t>Q28</t>
-  </si>
-  <si>
-    <t>בקבוצה חברתית אני מסוגל בקלות לעקוב אחר כמה וכמה שיחות של אנשים</t>
-  </si>
-  <si>
-    <t>AQ_10</t>
-  </si>
-  <si>
-    <t>Q29</t>
-  </si>
-  <si>
-    <t>אני מסתדר בקלות בסיטואציות חברתיות</t>
-  </si>
-  <si>
-    <t>AQ_11</t>
-  </si>
-  <si>
-    <t>Q30</t>
-  </si>
-  <si>
-    <t>אני נוטה להבחין בפרטים שאחרים אינם מבחינים בהם</t>
-  </si>
-  <si>
-    <t>AQ_12</t>
-  </si>
-  <si>
-    <t>Q31</t>
-  </si>
-  <si>
-    <t>אני מעדיף בילוי בספרייה על פני בילוי במסיבה</t>
-  </si>
-  <si>
-    <t>AQ_13</t>
-  </si>
-  <si>
-    <t>Q32</t>
-  </si>
-  <si>
-    <t>קל לי להמציא סיפורים</t>
-  </si>
-  <si>
-    <t>AQ_14</t>
-  </si>
-  <si>
-    <t>Q33</t>
-  </si>
-  <si>
-    <t>אני נמשך לבני-אדם יותר מאשר לחפצים</t>
-  </si>
-  <si>
-    <t>AQ_15</t>
-  </si>
-  <si>
-    <t>Q34</t>
-  </si>
-  <si>
-    <t>יש לי תחומי עניין מוגדרים היטב ואני מתעצבן כשאני לא יכול לעסוק בהם</t>
-  </si>
-  <si>
-    <t>AQ_16</t>
-  </si>
-  <si>
-    <t>Q35</t>
-  </si>
-  <si>
-    <t>אני נהנה משיחת חולין חברתית</t>
-  </si>
-  <si>
-    <t>AQ_17</t>
-  </si>
-  <si>
-    <t>Q36</t>
-  </si>
-  <si>
-    <t>כשאני מדבר, לא תמיד קל לאחרים להשחיל מילה</t>
-  </si>
-  <si>
-    <t>AQ_18</t>
-  </si>
-  <si>
-    <t>Q37</t>
-  </si>
-  <si>
-    <t>מספרים מרתקים אותי</t>
-  </si>
-  <si>
-    <t>AQ_19</t>
-  </si>
-  <si>
-    <t>Q38</t>
-  </si>
-  <si>
-    <t>כשאני קורא סיפור, קשה לי להבין את כוונותיהן של הדמויות</t>
-  </si>
-  <si>
-    <t>AQ_20</t>
-  </si>
-  <si>
-    <t>Q39</t>
-  </si>
-  <si>
-    <t>אני לא כל-כך נהנה לקרוא ספרות יפה</t>
-  </si>
-  <si>
-    <t>AQ_21</t>
-  </si>
-  <si>
-    <t>Q40</t>
-  </si>
-  <si>
-    <t>קשה לי לרכוש חברים חדשים</t>
-  </si>
-  <si>
-    <t>AQ_22</t>
-  </si>
-  <si>
-    <t>Q41</t>
-  </si>
-  <si>
-    <t>אני שם לב לדפוסים בכל מיני דברים כל הזמן</t>
-  </si>
-  <si>
-    <t>AQ_23</t>
-  </si>
-  <si>
-    <t>Q42</t>
-  </si>
-  <si>
-    <t>אני מעדיף בילוי בתיאטרון על פני בילוי במוזיאון</t>
-  </si>
-  <si>
-    <t>AQ_24</t>
-  </si>
-  <si>
-    <t>Q43</t>
-  </si>
-  <si>
-    <t>אני לא מוטרד כששגרת היום שלי מופרת</t>
-  </si>
-  <si>
-    <t>AQ_25</t>
-  </si>
-  <si>
-    <t>Q44</t>
-  </si>
-  <si>
-    <t>לעתים קרובות מתברר לי שאני לא יודע להחזיק שיחה שלא תדעך</t>
-  </si>
-  <si>
-    <t>AQ_26</t>
-  </si>
-  <si>
-    <t>Q45</t>
-  </si>
-  <si>
-    <t>קל לי "לקרוא בין השורות" כשמישהו מדבר אלי</t>
-  </si>
-  <si>
-    <t>AQ_27</t>
-  </si>
-  <si>
-    <t>Q46</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני מתרכז בתמונה כולה ולא בפרטים הקטנים</t>
-  </si>
-  <si>
-    <t>AQ_28</t>
-  </si>
-  <si>
-    <t>Q47</t>
-  </si>
-  <si>
-    <t>אין לי זיכרון טוב למספרי טלפון</t>
-  </si>
-  <si>
-    <t>AQ_29</t>
-  </si>
-  <si>
-    <t>Q48</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני לא מבחין בשינויים קלים בסיטואציה או במראהו של אדם אחר</t>
-  </si>
-  <si>
-    <t>AQ_30</t>
-  </si>
-  <si>
-    <t>Q49</t>
-  </si>
-  <si>
-    <t>אני מבחין מיד כשאדם שמקשיב לי מתחיל להשתעמם</t>
-  </si>
-  <si>
-    <t>AQ_31</t>
-  </si>
-  <si>
-    <t>Q50</t>
-  </si>
-  <si>
-    <t>קל לי לעשות כמה דברים בבת אחת</t>
-  </si>
-  <si>
-    <t>AQ_32</t>
-  </si>
-  <si>
-    <t>Q51</t>
-  </si>
-  <si>
-    <t>כשאני מדבר בטלפון, אני לא בטוח מתי תורי לדבר</t>
-  </si>
-  <si>
-    <t>AQ_33</t>
-  </si>
-  <si>
-    <t>Q52</t>
-  </si>
-  <si>
-    <t>אני נהנה לעשות דברים באופן ספונטני</t>
-  </si>
-  <si>
-    <t>AQ_34</t>
-  </si>
-  <si>
-    <t>Q53</t>
-  </si>
-  <si>
-    <t>לא פעם אני האחרון שמבין בדיחה</t>
-  </si>
-  <si>
-    <t>AQ_35</t>
-  </si>
-  <si>
-    <t>Q54</t>
-  </si>
-  <si>
-    <t>אני מבחין בקלות מה אדם אחר חושב או מרגיש ממראה פניו בלבד</t>
-  </si>
-  <si>
-    <t>AQ_36</t>
-  </si>
-  <si>
-    <t>Q55</t>
-  </si>
-  <si>
-    <t>כשמפריעים לי, אני יכול לחזור למה שעשיתי לפני כן במהירות רבה</t>
-  </si>
-  <si>
-    <t>AQ_37</t>
-  </si>
-  <si>
-    <t>Q56</t>
-  </si>
-  <si>
-    <t>אני טוב בשיחת חולין חברתית</t>
-  </si>
-  <si>
-    <t>AQ_38</t>
-  </si>
-  <si>
-    <t>Q57</t>
-  </si>
-  <si>
-    <t>אנשים אומרים לי פעמים רבות שאני מדבר עוד ועוד על אותו הדבר</t>
-  </si>
-  <si>
-    <t>AQ_39</t>
-  </si>
-  <si>
-    <t>Q58</t>
-  </si>
-  <si>
-    <t>כשהייתי צעיר נהניתי לשחק עם ילדים אחרים במשחקי דימיון</t>
-  </si>
-  <si>
-    <t>AQ_40</t>
-  </si>
-  <si>
-    <t>Q59</t>
-  </si>
-  <si>
-    <t>('אני אוהב לאסוף מידע על סוגים של דברים (למשל, סוגי מכוניות, מיני ציפורים, סוגי רכבות, מיני צמחים וכו</t>
-  </si>
-  <si>
-    <t>AQ_41</t>
-  </si>
-  <si>
-    <t>Q60</t>
-  </si>
-  <si>
-    <t>קשה לי לדמיין איך זה להיות אדם אחר</t>
-  </si>
-  <si>
-    <t>AQ_42</t>
-  </si>
-  <si>
-    <t>Q61</t>
-  </si>
-  <si>
-    <t>אני אוהב לתכנן בקפידה כל פעילות שאני משתתף בה</t>
-  </si>
-  <si>
-    <t>AQ_43</t>
-  </si>
-  <si>
-    <t>Q62</t>
-  </si>
-  <si>
-    <t>אני נהנה מאירועים חברתיים</t>
-  </si>
-  <si>
-    <t>AQ_44</t>
-  </si>
-  <si>
-    <t>Q63</t>
-  </si>
-  <si>
-    <t>אני מתקשה להבין את כוונותיהם של אנשים אחרים</t>
-  </si>
-  <si>
-    <t>AQ_45</t>
-  </si>
-  <si>
-    <t>Q64</t>
-  </si>
-  <si>
-    <t>מצבים חדשים מעוררים בי חרדה</t>
-  </si>
-  <si>
-    <t>AQ_46</t>
-  </si>
-  <si>
-    <t>Q65</t>
-  </si>
-  <si>
-    <t>אני נהנה להכיר אנשים חדשים</t>
-  </si>
-  <si>
-    <t>AQ_47</t>
-  </si>
-  <si>
-    <t>Q66</t>
-  </si>
-  <si>
-    <t>אני דיפלומט טוב</t>
-  </si>
-  <si>
-    <t>AQ_48</t>
-  </si>
-  <si>
-    <t>Q67</t>
-  </si>
-  <si>
-    <t>אני לא מצטיין בזכירת ימי ההולדת של אנשים אחרים</t>
-  </si>
-  <si>
-    <t>AQ_49</t>
-  </si>
-  <si>
-    <t>Q68</t>
-  </si>
-  <si>
-    <t>קל לי מאוד לשחק עם ילדים במשחקים שכרוכים בהעמדת פנים</t>
-  </si>
-  <si>
-    <t>AQ_50</t>
-  </si>
-  <si>
-    <t>Q108</t>
-  </si>
-  <si>
-    <t>אני מעדיפה לעשות דברים יחד עם אחרים ולא לבדי</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>Q109</t>
-  </si>
-  <si>
-    <t>אני מעדיפה לעשות דברים באותו האופן שוב ושוב</t>
-  </si>
-  <si>
-    <t>Q110</t>
-  </si>
-  <si>
-    <t>Q111</t>
-  </si>
-  <si>
-    <t>לעתים קרובות אני שוקעת עמוק כל-כך בדבר אחד עד שאני מפסיקה לראות דברים אחרים</t>
-  </si>
-  <si>
-    <t>Q112</t>
-  </si>
-  <si>
-    <t>לעיתים אני שמה לב לקולות חלשים שאחרים אינם שמים לב אליהם</t>
-  </si>
-  <si>
-    <t>Q113</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני שמה לב למספרי מכוניות או לפרטי מידע דומים</t>
-  </si>
-  <si>
-    <t>Q114</t>
-  </si>
-  <si>
-    <t>אנשים אומרים לי פעמים רבות שמה שאמרתי לא מנומס, אף על פי שלי נראה שהייתי מנומסת</t>
-  </si>
-  <si>
-    <t>Q115</t>
-  </si>
-  <si>
-    <t>כשאני קוראת סיפור אני יכולה לדמיין לי בקלות איך נראות הדמויות</t>
-  </si>
-  <si>
-    <t>Q116</t>
-  </si>
-  <si>
-    <t>Q117</t>
-  </si>
-  <si>
-    <t>בקבוצה חברתית אני מסוגלת בקלות לעקוב אחר כמה וכמה שיחות של אנשים</t>
-  </si>
-  <si>
-    <t>Q118</t>
-  </si>
-  <si>
-    <t>אני מסתדרת בקלות בסיטואציות חברתיות</t>
-  </si>
-  <si>
-    <t>Q119</t>
-  </si>
-  <si>
-    <t>Q120</t>
-  </si>
-  <si>
-    <t>אני מעדיפה בילוי בספרייה על פני בילוי במסיבה</t>
-  </si>
-  <si>
-    <t>Q121</t>
-  </si>
-  <si>
-    <t>Q122</t>
-  </si>
-  <si>
-    <t>אני נמשכת לבני-אדם יותר מאשר לחפצים</t>
-  </si>
-  <si>
-    <t>Q123</t>
-  </si>
-  <si>
-    <t>יש לי תחומי עניין מוגדרים היטב ואני מתעצבנת כשאני לא יכולה לעסוק בהם</t>
-  </si>
-  <si>
-    <t>Q124</t>
-  </si>
-  <si>
-    <t>אני נהנית משיחת חולין חברתית</t>
-  </si>
-  <si>
-    <t>Q125</t>
-  </si>
-  <si>
-    <t>כשאני מדברת, לא תמיד קל לאחרים להשחיל מילה</t>
-  </si>
-  <si>
-    <t>Q126</t>
-  </si>
-  <si>
-    <t>Q127</t>
-  </si>
-  <si>
-    <t>כשאני קוראת סיפור, קשה לי להבין את כוונותיהן של הדמויות</t>
-  </si>
-  <si>
-    <t>Q128</t>
-  </si>
-  <si>
-    <t>אני לא כל-כך נהנת לקרוא ספרות יפה</t>
-  </si>
-  <si>
-    <t>Q129</t>
-  </si>
-  <si>
-    <t>Q130</t>
-  </si>
-  <si>
-    <t>אני שמה לב לדפוסים בכל מיני דברים כל הזמן</t>
-  </si>
-  <si>
-    <t>Q131</t>
-  </si>
-  <si>
-    <t>אני מעדיפה בילוי בתיאטרון על פני בילוי במוזיאון</t>
-  </si>
-  <si>
-    <t>Q132</t>
-  </si>
-  <si>
-    <t>אני לא מוטרדת כששגרת היום שלי מופרת</t>
-  </si>
-  <si>
-    <t>Q133</t>
-  </si>
-  <si>
-    <t>לעתים קרובות מתברר לי שאני לא יודעת להחזיק שיחה שלא תדעך</t>
-  </si>
-  <si>
-    <t>Q134</t>
-  </si>
-  <si>
-    <t>Q135</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני מתרכזת בתמונה כולה ולא בפרטים הקטנים</t>
-  </si>
-  <si>
-    <t>Q136</t>
-  </si>
-  <si>
-    <t>Q137</t>
-  </si>
-  <si>
-    <t>בדרך-כלל אני לא מבחינה בשינויים קלים בסיטואציה או במראהו של אדם אחר</t>
-  </si>
-  <si>
-    <t>Q138</t>
-  </si>
-  <si>
-    <t>אני מבחינה מיד כשאדם שמקשיב לי מתחיל להשתעמם</t>
-  </si>
-  <si>
-    <t>Q139</t>
-  </si>
-  <si>
-    <t>Q140</t>
-  </si>
-  <si>
-    <t>כשאני מדברת בטלפון, אני לא בטוחה מתי תורי לדבר</t>
-  </si>
-  <si>
-    <t>Q141</t>
-  </si>
-  <si>
-    <t>אני נהנת לעשות דברים באופן ספונטני</t>
-  </si>
-  <si>
-    <t>Q142</t>
-  </si>
-  <si>
-    <t>לא פעם אני האחרונה שמבינה בדיחה</t>
-  </si>
-  <si>
-    <t>Q143</t>
-  </si>
-  <si>
-    <t>אני מבחינה בקלות מה אדם אחר חושב או מרגיש ממראה פניו בלבד</t>
-  </si>
-  <si>
-    <t>Q144</t>
-  </si>
-  <si>
-    <t>כשמפריעים לי, אני יכולה לחזור למה שעשיתי לפני כן במהירות רבה</t>
-  </si>
-  <si>
-    <t>Q145</t>
-  </si>
-  <si>
-    <t>אני טובה בשיחת חולין חברתית</t>
-  </si>
-  <si>
-    <t>Q146</t>
-  </si>
-  <si>
-    <t>אנשים אומרים לי פעמים רבות שאני מדברת עוד ועוד על אותו הדבר</t>
-  </si>
-  <si>
-    <t>Q147</t>
-  </si>
-  <si>
-    <t>כשהייתי צעירה נהניתי לשחק עם ילדים אחרים במשחקי דמיון</t>
-  </si>
-  <si>
-    <t>Q148</t>
-  </si>
-  <si>
-    <t>('אני אוהבת לאסוף מידע על סוגים של דברים (למשל, סוגי מכוניות, מיני ציפורים, סוגי רכבות, מיני צמחים וכו</t>
-  </si>
-  <si>
-    <t>Q149</t>
-  </si>
-  <si>
-    <t>Q150</t>
-  </si>
-  <si>
-    <t>אני אוהבת לתכנן בקפידה כל פעילות שאני משתתפת בה</t>
-  </si>
-  <si>
-    <t>Q151</t>
-  </si>
-  <si>
-    <t>אני נהנית מאירועים חברתיים</t>
-  </si>
-  <si>
-    <t>Q152</t>
-  </si>
-  <si>
-    <t>Q153</t>
-  </si>
-  <si>
-    <t>Q154</t>
-  </si>
-  <si>
-    <t>אני נהנית להכיר אנשים חדשים</t>
-  </si>
-  <si>
-    <t>Q155</t>
-  </si>
-  <si>
-    <t>אני דיפלומטית טובה</t>
-  </si>
-  <si>
-    <t>Q156</t>
-  </si>
-  <si>
-    <t>אני לא מצטיינת בזכירת ימי ההולדת של אנשים אחרים</t>
-  </si>
-  <si>
-    <t>Q157</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>אנא הזינו את מספר הנבדק שקיבלתם במייל</t>
   </si>
   <si>
     <t>demog-health</t>
@@ -1229,9 +1232,6 @@
   </si>
   <si>
     <t>אני מבולבל לגבי מה שאני מרגיש</t>
-  </si>
-  <si>
-    <t>second-questionnaire</t>
   </si>
   <si>
     <t>כשאני נסער, אני מרגיש שאני מאבד שליטה</t>
@@ -2650,10 +2650,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="5" max="5" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5598,7 +5599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5652,10 +5653,10 @@
         <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -5664,27 +5665,27 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J2">
         <v>0.31372549019607843</v>
       </c>
       <c r="K2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -5693,27 +5694,27 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J3">
         <v>0.26315789473684209</v>
       </c>
       <c r="K3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -5722,27 +5723,27 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J4">
         <v>0.14814814814814811</v>
       </c>
       <c r="K4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -5751,30 +5752,30 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J5">
         <v>0.25</v>
       </c>
       <c r="K5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -5783,33 +5784,33 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J6">
         <v>0.25</v>
       </c>
       <c r="K6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -5818,30 +5819,30 @@
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J7">
         <v>0.25</v>
       </c>
       <c r="K7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -5850,33 +5851,33 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J8">
         <v>0.4</v>
       </c>
       <c r="K8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
         <v>273</v>
       </c>
-      <c r="B9" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" t="s">
-        <v>276</v>
-      </c>
-      <c r="D9" t="s">
-        <v>272</v>
-      </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -5885,27 +5886,27 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J9">
         <v>0.4</v>
       </c>
       <c r="K9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -5914,27 +5915,27 @@
         <v>7</v>
       </c>
       <c r="I10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J10">
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="K10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -5943,27 +5944,27 @@
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J11">
         <v>0.17391304347826089</v>
       </c>
       <c r="K11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -5972,7 +5973,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -5983,16 +5984,16 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -6001,7 +6002,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -6012,16 +6013,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -6030,7 +6031,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -6041,22 +6042,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -6065,7 +6066,7 @@
         <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -6076,22 +6077,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -6100,7 +6101,7 @@
         <v>13</v>
       </c>
       <c r="I16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -6111,22 +6112,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -6135,7 +6136,7 @@
         <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -6146,22 +6147,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -6170,7 +6171,7 @@
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -6181,22 +6182,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -6205,7 +6206,7 @@
         <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -6216,22 +6217,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -6240,7 +6241,7 @@
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -6251,19 +6252,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
@@ -6272,7 +6273,7 @@
         <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -6283,22 +6284,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -6307,7 +6308,7 @@
         <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -6318,19 +6319,19 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -6339,7 +6340,7 @@
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J23">
         <v>0.95833333333333337</v>
@@ -6350,22 +6351,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -6374,7 +6375,7 @@
         <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J24">
         <v>0.95833333333333337</v>
@@ -6385,22 +6386,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -6409,7 +6410,7 @@
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J25">
         <v>0.97222222222222221</v>
@@ -6420,22 +6421,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B26" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C26" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -6444,7 +6445,7 @@
         <v>23</v>
       </c>
       <c r="I26" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J26">
         <v>0.97222222222222221</v>
@@ -6455,22 +6456,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C27" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D27" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -6479,7 +6480,7 @@
         <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J27">
         <v>0.97222222222222221</v>
@@ -6490,22 +6491,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D28" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -6514,7 +6515,7 @@
         <v>25</v>
       </c>
       <c r="I28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J28">
         <v>0.97222222222222221</v>
@@ -6525,22 +6526,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C29" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -6549,7 +6550,7 @@
         <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J29">
         <v>0.97222222222222221</v>
@@ -6560,16 +6561,16 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -6578,7 +6579,7 @@
         <v>27</v>
       </c>
       <c r="I30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -6589,16 +6590,16 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G31" t="s">
         <v>167</v>
@@ -6607,27 +6608,27 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J31">
         <v>0.31372549019607843</v>
       </c>
       <c r="K31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G32" t="s">
         <v>167</v>
@@ -6636,27 +6637,27 @@
         <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J32">
         <v>0.26315789473684209</v>
       </c>
       <c r="K32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G33" t="s">
         <v>167</v>
@@ -6665,30 +6666,30 @@
         <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J33">
         <v>0.14814814814814811</v>
       </c>
       <c r="K33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G34" t="s">
         <v>167</v>
@@ -6697,33 +6698,33 @@
         <v>4</v>
       </c>
       <c r="I34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J34">
         <v>0.25</v>
       </c>
       <c r="K34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G35" t="s">
         <v>167</v>
@@ -6732,30 +6733,30 @@
         <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J35">
         <v>0.25</v>
       </c>
       <c r="K35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G36" t="s">
         <v>167</v>
@@ -6764,33 +6765,33 @@
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J36">
         <v>0.25</v>
       </c>
       <c r="K36" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>349</v>
+      </c>
+      <c r="B37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37" t="s">
+        <v>350</v>
+      </c>
+      <c r="D37" t="s">
         <v>348</v>
       </c>
-      <c r="B37" t="s">
-        <v>274</v>
-      </c>
-      <c r="C37" t="s">
-        <v>349</v>
-      </c>
-      <c r="D37" t="s">
-        <v>347</v>
-      </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G37" t="s">
         <v>167</v>
@@ -6799,27 +6800,27 @@
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J37">
         <v>0.25</v>
       </c>
       <c r="K37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G38" t="s">
         <v>167</v>
@@ -6828,27 +6829,27 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J38">
         <v>0.4</v>
       </c>
       <c r="K38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G39" t="s">
         <v>167</v>
@@ -6857,27 +6858,27 @@
         <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J39">
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="K39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F40" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G40" t="s">
         <v>167</v>
@@ -6886,27 +6887,27 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J40">
         <v>0.17391304347826089</v>
       </c>
       <c r="K40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G41" t="s">
         <v>167</v>
@@ -6915,7 +6916,7 @@
         <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -6926,16 +6927,16 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G42" t="s">
         <v>167</v>
@@ -6944,7 +6945,7 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -6955,16 +6956,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G43" t="s">
         <v>167</v>
@@ -6973,7 +6974,7 @@
         <v>11</v>
       </c>
       <c r="I43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -6984,22 +6985,22 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C44" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D44" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G44" t="s">
         <v>167</v>
@@ -7008,7 +7009,7 @@
         <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -7019,22 +7020,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C45" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D45" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G45" t="s">
         <v>167</v>
@@ -7043,7 +7044,7 @@
         <v>13</v>
       </c>
       <c r="I45" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -7054,22 +7055,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C46" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G46" t="s">
         <v>167</v>
@@ -7078,7 +7079,7 @@
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -7089,22 +7090,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C47" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D47" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G47" t="s">
         <v>167</v>
@@ -7113,7 +7114,7 @@
         <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -7124,22 +7125,22 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G48" t="s">
         <v>167</v>
@@ -7148,7 +7149,7 @@
         <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -7159,22 +7160,22 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C49" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D49" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G49" t="s">
         <v>167</v>
@@ -7183,7 +7184,7 @@
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -7194,19 +7195,19 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F50" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G50" t="s">
         <v>167</v>
@@ -7215,7 +7216,7 @@
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -7226,22 +7227,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C51" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G51" t="s">
         <v>167</v>
@@ -7250,7 +7251,7 @@
         <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -7261,19 +7262,19 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F52" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G52" t="s">
         <v>167</v>
@@ -7282,7 +7283,7 @@
         <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J52">
         <v>0.95833333333333337</v>
@@ -7293,22 +7294,22 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C53" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F53" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G53" t="s">
         <v>167</v>
@@ -7317,7 +7318,7 @@
         <v>21</v>
       </c>
       <c r="I53" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J53">
         <v>0.95833333333333337</v>
@@ -7328,22 +7329,22 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D54" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G54" t="s">
         <v>167</v>
@@ -7352,7 +7353,7 @@
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J54">
         <v>0.97222222222222221</v>
@@ -7363,22 +7364,22 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D55" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G55" t="s">
         <v>167</v>
@@ -7387,7 +7388,7 @@
         <v>23</v>
       </c>
       <c r="I55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J55">
         <v>0.97222222222222221</v>
@@ -7398,22 +7399,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D56" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G56" t="s">
         <v>167</v>
@@ -7422,7 +7423,7 @@
         <v>24</v>
       </c>
       <c r="I56" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J56">
         <v>0.97222222222222221</v>
@@ -7433,22 +7434,22 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B57" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G57" t="s">
         <v>167</v>
@@ -7457,7 +7458,7 @@
         <v>25</v>
       </c>
       <c r="I57" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J57">
         <v>0.97222222222222221</v>
@@ -7468,22 +7469,22 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C58" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D58" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G58" t="s">
         <v>167</v>
@@ -7492,7 +7493,7 @@
         <v>26</v>
       </c>
       <c r="I58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J58">
         <v>0.97222222222222221</v>
@@ -7503,16 +7504,16 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G59" t="s">
         <v>167</v>
@@ -7521,7 +7522,7 @@
         <v>27</v>
       </c>
       <c r="I59" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -7536,7 +7537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -7580,13 +7581,13 @@
         <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -7595,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -7609,13 +7610,13 @@
         <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -7624,7 +7625,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J3">
         <v>0.98461538461538467</v>
@@ -7638,13 +7639,13 @@
         <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -7653,7 +7654,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J4">
         <v>0.96153846153846156</v>
@@ -7667,13 +7668,13 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -7682,7 +7683,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J5">
         <v>0.9555555555555556</v>
@@ -7696,13 +7697,13 @@
         <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -7711,7 +7712,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J6">
         <v>0.9438202247191011</v>
@@ -7725,13 +7726,13 @@
         <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -7740,7 +7741,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J7">
         <v>0.98765432098765427</v>
@@ -7754,13 +7755,13 @@
         <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -7769,7 +7770,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J8">
         <v>0.96470588235294119</v>
@@ -7783,13 +7784,13 @@
         <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -7798,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J9">
         <v>0.98734177215189878</v>
@@ -7809,16 +7810,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E10" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -7827,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J10">
         <v>0.96666666666666667</v>
@@ -7838,16 +7839,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B11" t="s">
         <v>400</v>
       </c>
       <c r="E11" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -7856,7 +7857,7 @@
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J11">
         <v>0.96</v>
@@ -7867,16 +7868,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B12" t="s">
         <v>401</v>
       </c>
       <c r="E12" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -7885,7 +7886,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J12">
         <v>0.95081967213114749</v>
@@ -7896,16 +7897,16 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B13" t="s">
         <v>402</v>
       </c>
       <c r="E13" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -7914,7 +7915,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J13">
         <v>0.96453900709219853</v>
@@ -7925,16 +7926,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B14" t="s">
         <v>403</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -7943,7 +7944,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J14">
         <v>0.9438202247191011</v>
@@ -7954,16 +7955,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B15" t="s">
         <v>404</v>
       </c>
       <c r="E15" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -7972,7 +7973,7 @@
         <v>6</v>
       </c>
       <c r="I15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J15">
         <v>0.97727272727272729</v>
@@ -7983,16 +7984,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
         <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -8001,7 +8002,7 @@
         <v>7</v>
       </c>
       <c r="I16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J16">
         <v>0.98701298701298701</v>
@@ -8012,16 +8013,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
         <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -8030,7 +8031,7 @@
         <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J17">
         <v>0.9850746268656716</v>
@@ -8044,13 +8045,13 @@
         <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G18" t="s">
         <v>167</v>
@@ -8059,7 +8060,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -8076,10 +8077,10 @@
         <v>407</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G19" t="s">
         <v>167</v>
@@ -8088,7 +8089,7 @@
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J19">
         <v>0.98461538461538467</v>
@@ -8105,10 +8106,10 @@
         <v>408</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G20" t="s">
         <v>167</v>
@@ -8117,7 +8118,7 @@
         <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J20">
         <v>0.96153846153846156</v>
@@ -8134,10 +8135,10 @@
         <v>409</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G21" t="s">
         <v>167</v>
@@ -8146,7 +8147,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J21">
         <v>0.9555555555555556</v>
@@ -8163,10 +8164,10 @@
         <v>410</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G22" t="s">
         <v>167</v>
@@ -8175,7 +8176,7 @@
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J22">
         <v>0.9438202247191011</v>
@@ -8192,10 +8193,10 @@
         <v>411</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F23" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G23" t="s">
         <v>167</v>
@@ -8204,7 +8205,7 @@
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J23">
         <v>0.98765432098765427</v>
@@ -8221,10 +8222,10 @@
         <v>412</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G24" t="s">
         <v>167</v>
@@ -8233,7 +8234,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J24">
         <v>0.96470588235294119</v>
@@ -8250,10 +8251,10 @@
         <v>413</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F25" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G25" t="s">
         <v>167</v>
@@ -8262,7 +8263,7 @@
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J25">
         <v>0.98734177215189878</v>
@@ -8279,10 +8280,10 @@
         <v>415</v>
       </c>
       <c r="E26" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G26" t="s">
         <v>167</v>
@@ -8291,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J26">
         <v>0.96666666666666667</v>
@@ -8308,10 +8309,10 @@
         <v>417</v>
       </c>
       <c r="E27" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G27" t="s">
         <v>167</v>
@@ -8320,7 +8321,7 @@
         <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J27">
         <v>0.96</v>
@@ -8337,10 +8338,10 @@
         <v>419</v>
       </c>
       <c r="E28" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G28" t="s">
         <v>167</v>
@@ -8349,7 +8350,7 @@
         <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J28">
         <v>0.95081967213114749</v>
@@ -8366,10 +8367,10 @@
         <v>421</v>
       </c>
       <c r="E29" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G29" t="s">
         <v>167</v>
@@ -8378,7 +8379,7 @@
         <v>4</v>
       </c>
       <c r="I29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J29">
         <v>0.96453900709219853</v>
@@ -8395,10 +8396,10 @@
         <v>423</v>
       </c>
       <c r="E30" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G30" t="s">
         <v>167</v>
@@ -8407,7 +8408,7 @@
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J30">
         <v>0.9438202247191011</v>
@@ -8424,10 +8425,10 @@
         <v>425</v>
       </c>
       <c r="E31" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G31" t="s">
         <v>167</v>
@@ -8436,7 +8437,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J31">
         <v>0.97727272727272729</v>
@@ -8453,10 +8454,10 @@
         <v>427</v>
       </c>
       <c r="E32" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G32" t="s">
         <v>167</v>
@@ -8465,7 +8466,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J32">
         <v>0.98701298701298701</v>
@@ -8482,10 +8483,10 @@
         <v>429</v>
       </c>
       <c r="E33" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G33" t="s">
         <v>167</v>
@@ -8494,7 +8495,7 @@
         <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J33">
         <v>0.9850746268656716</v>
@@ -8509,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8560,7 +8561,7 @@
         <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>431</v>
@@ -8589,7 +8590,7 @@
         <v>433</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>431</v>
@@ -8618,7 +8619,7 @@
         <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>431</v>
@@ -8647,7 +8648,7 @@
         <v>437</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>431</v>
@@ -8676,7 +8677,7 @@
         <v>439</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>431</v>
@@ -8705,7 +8706,7 @@
         <v>441</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>431</v>
@@ -8734,7 +8735,7 @@
         <v>443</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
         <v>431</v>
@@ -8763,7 +8764,7 @@
         <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>431</v>
@@ -8792,7 +8793,7 @@
         <v>447</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
         <v>431</v>
@@ -8821,7 +8822,7 @@
         <v>449</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F11" t="s">
         <v>431</v>
@@ -8850,7 +8851,7 @@
         <v>451</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
         <v>431</v>
@@ -8879,7 +8880,7 @@
         <v>453</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
         <v>431</v>
@@ -8908,7 +8909,7 @@
         <v>455</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F14" t="s">
         <v>431</v>
@@ -8937,7 +8938,7 @@
         <v>457</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
         <v>431</v>
@@ -8966,7 +8967,7 @@
         <v>459</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
         <v>431</v>
@@ -8995,7 +8996,7 @@
         <v>461</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F17" t="s">
         <v>431</v>
@@ -9018,13 +9019,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B18" t="s">
         <v>463</v>
       </c>
       <c r="E18" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
         <v>431</v>
@@ -9047,13 +9048,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B19" t="s">
         <v>464</v>
       </c>
       <c r="E19" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>431</v>
@@ -9076,13 +9077,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B20" t="s">
         <v>465</v>
       </c>
       <c r="E20" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>431</v>
@@ -9105,13 +9106,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B21" t="s">
         <v>466</v>
       </c>
       <c r="E21" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
         <v>431</v>
@@ -9134,13 +9135,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B22" t="s">
         <v>467</v>
       </c>
       <c r="E22" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>431</v>
@@ -9163,13 +9164,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B23" t="s">
         <v>468</v>
       </c>
       <c r="E23" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s">
         <v>431</v>
@@ -9192,13 +9193,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B24" t="s">
         <v>469</v>
       </c>
       <c r="E24" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
         <v>431</v>
@@ -9221,13 +9222,13 @@
     </row>
     <row r="25" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>470</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>431</v>
@@ -9245,18 +9246,18 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s">
         <v>471</v>
       </c>
       <c r="E26" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
         <v>431</v>
@@ -9279,13 +9280,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s">
         <v>472</v>
       </c>
       <c r="E27" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
         <v>431</v>
@@ -9308,13 +9309,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B28" t="s">
         <v>473</v>
       </c>
       <c r="E28" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
         <v>431</v>
@@ -9337,13 +9338,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s">
         <v>474</v>
       </c>
       <c r="E29" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
         <v>431</v>
@@ -9366,13 +9367,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s">
         <v>475</v>
       </c>
       <c r="E30" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
         <v>431</v>
@@ -9395,13 +9396,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s">
         <v>476</v>
       </c>
       <c r="E31" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
         <v>431</v>
@@ -9430,7 +9431,7 @@
         <v>478</v>
       </c>
       <c r="E32" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>431</v>
@@ -9459,7 +9460,7 @@
         <v>480</v>
       </c>
       <c r="E33" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
         <v>431</v>
@@ -9488,7 +9489,7 @@
         <v>482</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F34" t="s">
         <v>431</v>
@@ -9517,7 +9518,7 @@
         <v>484</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F35" t="s">
         <v>431</v>
@@ -9546,7 +9547,7 @@
         <v>486</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F36" t="s">
         <v>431</v>
@@ -9575,7 +9576,7 @@
         <v>488</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F37" t="s">
         <v>431</v>
@@ -9604,7 +9605,7 @@
         <v>490</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F38" t="s">
         <v>431</v>
@@ -9633,7 +9634,7 @@
         <v>441</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
         <v>431</v>
@@ -9662,7 +9663,7 @@
         <v>493</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F40" t="s">
         <v>431</v>
@@ -9691,7 +9692,7 @@
         <v>495</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F41" t="s">
         <v>431</v>
@@ -9720,7 +9721,7 @@
         <v>496</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F42" t="s">
         <v>431</v>
@@ -9749,7 +9750,7 @@
         <v>497</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F43" t="s">
         <v>431</v>
@@ -9778,7 +9779,7 @@
         <v>498</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F44" t="s">
         <v>431</v>
@@ -9807,7 +9808,7 @@
         <v>499</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F45" t="s">
         <v>431</v>
@@ -9836,7 +9837,7 @@
         <v>500</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
         <v>431</v>
@@ -9865,7 +9866,7 @@
         <v>501</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F47" t="s">
         <v>431</v>
@@ -9894,7 +9895,7 @@
         <v>502</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
         <v>431</v>
@@ -9923,7 +9924,7 @@
         <v>461</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>431</v>
@@ -9946,13 +9947,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s">
         <v>463</v>
       </c>
       <c r="E50" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F50" t="s">
         <v>431</v>
@@ -9975,13 +9976,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s">
         <v>503</v>
       </c>
       <c r="E51" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F51" t="s">
         <v>431</v>
@@ -10004,13 +10005,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s">
         <v>504</v>
       </c>
       <c r="E52" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
         <v>431</v>
@@ -10033,13 +10034,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s">
         <v>466</v>
       </c>
       <c r="E53" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F53" t="s">
         <v>431</v>
@@ -10062,13 +10063,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s">
         <v>505</v>
       </c>
       <c r="E54" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F54" t="s">
         <v>431</v>
@@ -10091,13 +10092,13 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s">
         <v>506</v>
       </c>
       <c r="E55" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
         <v>431</v>
@@ -10126,7 +10127,7 @@
         <v>508</v>
       </c>
       <c r="E56" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F56" t="s">
         <v>431</v>
@@ -10155,7 +10156,7 @@
         <v>461</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>431</v>
@@ -10173,7 +10174,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -10184,7 +10185,7 @@
         <v>471</v>
       </c>
       <c r="E58" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F58" t="s">
         <v>431</v>
@@ -10213,7 +10214,7 @@
         <v>472</v>
       </c>
       <c r="E59" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F59" t="s">
         <v>431</v>
@@ -10242,7 +10243,7 @@
         <v>510</v>
       </c>
       <c r="E60" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
         <v>431</v>
@@ -10271,7 +10272,7 @@
         <v>511</v>
       </c>
       <c r="E61" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F61" t="s">
         <v>431</v>
@@ -10300,7 +10301,7 @@
         <v>512</v>
       </c>
       <c r="E62" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F62" t="s">
         <v>431</v>
@@ -10329,7 +10330,7 @@
         <v>513</v>
       </c>
       <c r="E63" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F63" t="s">
         <v>431</v>
@@ -10358,7 +10359,7 @@
         <v>514</v>
       </c>
       <c r="E64" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
         <v>431</v>
@@ -10387,7 +10388,7 @@
         <v>515</v>
       </c>
       <c r="E65" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F65" t="s">
         <v>431</v>
@@ -10414,7 +10415,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -10461,7 +10462,7 @@
         <v>516</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>517</v>
@@ -10490,7 +10491,7 @@
         <v>519</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>517</v>
@@ -10519,7 +10520,7 @@
         <v>521</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>517</v>
@@ -10548,7 +10549,7 @@
         <v>522</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>517</v>
@@ -10575,7 +10576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10633,7 +10634,7 @@
         <v>525</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>526</v>
@@ -10668,7 +10669,7 @@
         <v>529</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>526</v>
@@ -10703,7 +10704,7 @@
         <v>532</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>526</v>
@@ -10738,7 +10739,7 @@
         <v>535</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>526</v>
@@ -10773,7 +10774,7 @@
         <v>538</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>526</v>
@@ -10808,7 +10809,7 @@
         <v>541</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>526</v>
@@ -10843,7 +10844,7 @@
         <v>544</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
         <v>526</v>
@@ -10878,7 +10879,7 @@
         <v>547</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>526</v>
@@ -10913,7 +10914,7 @@
         <v>550</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
         <v>526</v>
@@ -10948,7 +10949,7 @@
         <v>553</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F11" t="s">
         <v>526</v>
@@ -10983,7 +10984,7 @@
         <v>557</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
         <v>526</v>
@@ -11018,7 +11019,7 @@
         <v>560</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
         <v>526</v>
@@ -11053,7 +11054,7 @@
         <v>563</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F14" t="s">
         <v>526</v>
@@ -11088,7 +11089,7 @@
         <v>566</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
         <v>526</v>
@@ -11123,7 +11124,7 @@
         <v>569</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
         <v>526</v>
@@ -11158,7 +11159,7 @@
         <v>572</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F17" t="s">
         <v>526</v>
@@ -11193,7 +11194,7 @@
         <v>575</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F18" t="s">
         <v>526</v>
@@ -11222,7 +11223,7 @@
         <v>577</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F19" t="s">
         <v>526</v>
@@ -11251,7 +11252,7 @@
         <v>579</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F20" t="s">
         <v>526</v>
@@ -11280,7 +11281,7 @@
         <v>581</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F21" t="s">
         <v>526</v>
@@ -11309,7 +11310,7 @@
         <v>583</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F22" t="s">
         <v>526</v>
@@ -11338,7 +11339,7 @@
         <v>585</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F23" t="s">
         <v>526</v>
@@ -11367,7 +11368,7 @@
         <v>588</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
         <v>526</v>
@@ -11396,7 +11397,7 @@
         <v>591</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F25" t="s">
         <v>526</v>
@@ -11425,7 +11426,7 @@
         <v>594</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F26" t="s">
         <v>526</v>
@@ -11454,7 +11455,7 @@
         <v>597</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F27" t="s">
         <v>526</v>
@@ -11483,7 +11484,7 @@
         <v>600</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F28" t="s">
         <v>526</v>
@@ -11512,7 +11513,7 @@
         <v>603</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F29" t="s">
         <v>526</v>
@@ -11541,7 +11542,7 @@
         <v>606</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F30" t="s">
         <v>526</v>
@@ -11570,7 +11571,7 @@
         <v>609</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F31" t="s">
         <v>526</v>
@@ -11599,7 +11600,7 @@
         <v>612</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F32" t="s">
         <v>526</v>
@@ -11628,7 +11629,7 @@
         <v>615</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F33" t="s">
         <v>526</v>
@@ -11657,7 +11658,7 @@
         <v>618</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F34" t="s">
         <v>526</v>
@@ -11686,7 +11687,7 @@
         <v>621</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F35" t="s">
         <v>526</v>
@@ -11715,7 +11716,7 @@
         <v>624</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F36" t="s">
         <v>526</v>
@@ -11744,7 +11745,7 @@
         <v>627</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F37" t="s">
         <v>526</v>
@@ -11773,7 +11774,7 @@
         <v>630</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F38" t="s">
         <v>526</v>
@@ -11808,7 +11809,7 @@
         <v>525</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
         <v>526</v>
@@ -11843,7 +11844,7 @@
         <v>529</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F40" t="s">
         <v>526</v>
@@ -11878,7 +11879,7 @@
         <v>532</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F41" t="s">
         <v>526</v>
@@ -11913,7 +11914,7 @@
         <v>535</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F42" t="s">
         <v>526</v>
@@ -11948,7 +11949,7 @@
         <v>538</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F43" t="s">
         <v>526</v>
@@ -11983,7 +11984,7 @@
         <v>541</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F44" t="s">
         <v>526</v>
@@ -12018,7 +12019,7 @@
         <v>544</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F45" t="s">
         <v>526</v>
@@ -12053,7 +12054,7 @@
         <v>547</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
         <v>526</v>
@@ -12088,7 +12089,7 @@
         <v>550</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F47" t="s">
         <v>526</v>
@@ -12123,7 +12124,7 @@
         <v>553</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
         <v>526</v>
@@ -12158,7 +12159,7 @@
         <v>557</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F49" t="s">
         <v>526</v>
@@ -12193,7 +12194,7 @@
         <v>560</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F50" t="s">
         <v>526</v>
@@ -12228,7 +12229,7 @@
         <v>563</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F51" t="s">
         <v>526</v>
@@ -12263,7 +12264,7 @@
         <v>566</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F52" t="s">
         <v>526</v>
@@ -12298,7 +12299,7 @@
         <v>569</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F53" t="s">
         <v>526</v>
@@ -12333,7 +12334,7 @@
         <v>572</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
         <v>526</v>
@@ -12368,7 +12369,7 @@
         <v>575</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F55" t="s">
         <v>526</v>
@@ -12397,7 +12398,7 @@
         <v>577</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F56" t="s">
         <v>526</v>
@@ -12426,7 +12427,7 @@
         <v>579</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F57" t="s">
         <v>526</v>
@@ -12455,7 +12456,7 @@
         <v>650</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F58" t="s">
         <v>526</v>
@@ -12484,7 +12485,7 @@
         <v>651</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F59" t="s">
         <v>526</v>
@@ -12513,7 +12514,7 @@
         <v>585</v>
       </c>
       <c r="E60" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F60" t="s">
         <v>526</v>
@@ -12542,7 +12543,7 @@
         <v>588</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F61" t="s">
         <v>526</v>
@@ -12571,7 +12572,7 @@
         <v>591</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F62" t="s">
         <v>526</v>
@@ -12600,7 +12601,7 @@
         <v>594</v>
       </c>
       <c r="E63" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F63" t="s">
         <v>526</v>
@@ -12629,7 +12630,7 @@
         <v>652</v>
       </c>
       <c r="E64" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F64" t="s">
         <v>526</v>
@@ -12658,7 +12659,7 @@
         <v>600</v>
       </c>
       <c r="E65" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F65" t="s">
         <v>526</v>
@@ -12687,7 +12688,7 @@
         <v>603</v>
       </c>
       <c r="E66" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F66" t="s">
         <v>526</v>
@@ -12716,7 +12717,7 @@
         <v>653</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F67" t="s">
         <v>526</v>
@@ -12745,7 +12746,7 @@
         <v>609</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F68" t="s">
         <v>526</v>
@@ -12774,7 +12775,7 @@
         <v>655</v>
       </c>
       <c r="E69" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F69" t="s">
         <v>526</v>
@@ -12803,7 +12804,7 @@
         <v>657</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F70" t="s">
         <v>526</v>
@@ -12832,7 +12833,7 @@
         <v>659</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F71" t="s">
         <v>526</v>
@@ -12861,7 +12862,7 @@
         <v>621</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F72" t="s">
         <v>526</v>
@@ -12890,7 +12891,7 @@
         <v>662</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F73" t="s">
         <v>526</v>
@@ -12919,7 +12920,7 @@
         <v>627</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F74" t="s">
         <v>526</v>
@@ -12948,7 +12949,7 @@
         <v>665</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F75" t="s">
         <v>526</v>
@@ -12975,7 +12976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -13022,7 +13023,7 @@
         <v>666</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>667</v>
@@ -13051,7 +13052,7 @@
         <v>669</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>667</v>
@@ -13080,7 +13081,7 @@
         <v>671</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>667</v>
@@ -13109,7 +13110,7 @@
         <v>673</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>667</v>
@@ -13138,7 +13139,7 @@
         <v>675</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>667</v>
@@ -13167,7 +13168,7 @@
         <v>677</v>
       </c>
       <c r="E7" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>667</v>
@@ -13196,7 +13197,7 @@
         <v>678</v>
       </c>
       <c r="E8" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>667</v>
@@ -13225,7 +13226,7 @@
         <v>679</v>
       </c>
       <c r="E9" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
         <v>667</v>
@@ -13254,7 +13255,7 @@
         <v>680</v>
       </c>
       <c r="E10" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
         <v>667</v>
@@ -13283,7 +13284,7 @@
         <v>681</v>
       </c>
       <c r="E11" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>667</v>
@@ -13312,7 +13313,7 @@
         <v>682</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F12" t="s">
         <v>667</v>
@@ -13341,7 +13342,7 @@
         <v>683</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
         <v>667</v>
@@ -13370,7 +13371,7 @@
         <v>684</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F14" t="s">
         <v>667</v>
@@ -13399,7 +13400,7 @@
         <v>685</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
         <v>667</v>
@@ -13428,7 +13429,7 @@
         <v>686</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
         <v>667</v>
@@ -13457,7 +13458,7 @@
         <v>687</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s">
         <v>667</v>
@@ -13486,7 +13487,7 @@
         <v>678</v>
       </c>
       <c r="E18" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
         <v>667</v>
@@ -13515,7 +13516,7 @@
         <v>679</v>
       </c>
       <c r="E19" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>667</v>
@@ -13544,7 +13545,7 @@
         <v>680</v>
       </c>
       <c r="E20" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>667</v>
@@ -13573,7 +13574,7 @@
         <v>688</v>
       </c>
       <c r="E21" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
         <v>667</v>
@@ -13600,7 +13601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -13647,7 +13648,7 @@
         <v>689</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>690</v>
@@ -13676,7 +13677,7 @@
         <v>692</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>690</v>
@@ -13705,7 +13706,7 @@
         <v>694</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>690</v>
@@ -13734,7 +13735,7 @@
         <v>696</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>690</v>
@@ -13763,7 +13764,7 @@
         <v>698</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>690</v>
@@ -13792,7 +13793,7 @@
         <v>700</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>690</v>
@@ -13821,7 +13822,7 @@
         <v>702</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
         <v>690</v>
@@ -13850,7 +13851,7 @@
         <v>704</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>690</v>
@@ -13879,7 +13880,7 @@
         <v>706</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
         <v>690</v>
@@ -13908,7 +13909,7 @@
         <v>708</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F11" t="s">
         <v>690</v>
@@ -13937,7 +13938,7 @@
         <v>710</v>
       </c>
       <c r="E12" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
         <v>690</v>
@@ -13966,7 +13967,7 @@
         <v>711</v>
       </c>
       <c r="E13" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>690</v>
@@ -13995,7 +13996,7 @@
         <v>712</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>690</v>
@@ -14024,7 +14025,7 @@
         <v>713</v>
       </c>
       <c r="E15" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
         <v>690</v>
@@ -14053,7 +14054,7 @@
         <v>714</v>
       </c>
       <c r="E16" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
         <v>690</v>
@@ -14082,7 +14083,7 @@
         <v>715</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s">
         <v>690</v>
@@ -14111,7 +14112,7 @@
         <v>716</v>
       </c>
       <c r="E18" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
         <v>690</v>
@@ -14140,7 +14141,7 @@
         <v>717</v>
       </c>
       <c r="E19" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>690</v>
@@ -14169,7 +14170,7 @@
         <v>718</v>
       </c>
       <c r="E20" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>690</v>
@@ -14198,7 +14199,7 @@
         <v>719</v>
       </c>
       <c r="E21" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
         <v>690</v>
@@ -14227,7 +14228,7 @@
         <v>720</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F22" t="s">
         <v>690</v>
@@ -14256,7 +14257,7 @@
         <v>721</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F23" t="s">
         <v>690</v>
@@ -14285,7 +14286,7 @@
         <v>722</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
         <v>690</v>
@@ -14314,7 +14315,7 @@
         <v>723</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F25" t="s">
         <v>690</v>
@@ -14343,7 +14344,7 @@
         <v>724</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F26" t="s">
         <v>690</v>
@@ -14372,7 +14373,7 @@
         <v>725</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F27" t="s">
         <v>690</v>
@@ -14401,7 +14402,7 @@
         <v>726</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F28" t="s">
         <v>690</v>
@@ -14430,7 +14431,7 @@
         <v>704</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F29" t="s">
         <v>690</v>
@@ -14459,7 +14460,7 @@
         <v>727</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F30" t="s">
         <v>690</v>
@@ -14488,7 +14489,7 @@
         <v>708</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F31" t="s">
         <v>690</v>
@@ -14517,7 +14518,7 @@
         <v>728</v>
       </c>
       <c r="E32" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>690</v>
@@ -14546,7 +14547,7 @@
         <v>729</v>
       </c>
       <c r="E33" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
         <v>690</v>
@@ -14575,7 +14576,7 @@
         <v>731</v>
       </c>
       <c r="E34" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
         <v>690</v>
@@ -14604,7 +14605,7 @@
         <v>713</v>
       </c>
       <c r="E35" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
         <v>690</v>
@@ -14633,7 +14634,7 @@
         <v>734</v>
       </c>
       <c r="E36" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
         <v>690</v>
@@ -14662,7 +14663,7 @@
         <v>736</v>
       </c>
       <c r="E37" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F37" t="s">
         <v>690</v>
@@ -14691,7 +14692,7 @@
         <v>738</v>
       </c>
       <c r="E38" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
         <v>690</v>
@@ -14720,7 +14721,7 @@
         <v>740</v>
       </c>
       <c r="E39" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
         <v>690</v>
@@ -14749,7 +14750,7 @@
         <v>718</v>
       </c>
       <c r="E40" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
         <v>690</v>
@@ -14778,7 +14779,7 @@
         <v>743</v>
       </c>
       <c r="E41" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
         <v>690</v>
@@ -14805,7 +14806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -14852,7 +14853,7 @@
         <v>744</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
         <v>745</v>
@@ -14881,7 +14882,7 @@
         <v>747</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F3" t="s">
         <v>745</v>
@@ -14910,7 +14911,7 @@
         <v>749</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
         <v>745</v>
@@ -14939,7 +14940,7 @@
         <v>751</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>745</v>
@@ -14968,7 +14969,7 @@
         <v>744</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
         <v>745</v>
@@ -14997,7 +14998,7 @@
         <v>747</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>745</v>
@@ -15026,7 +15027,7 @@
         <v>749</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
         <v>745</v>
@@ -15055,7 +15056,7 @@
         <v>753</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
         <v>745</v>
